--- a/imageCreationExcel/Bright/Master/MASTER_9.xlsx
+++ b/imageCreationExcel/Bright/Master/MASTER_9.xlsx
@@ -552,15 +552,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\8_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>M_9_1_1_unmatch_8_day_sun_empty_MODEL.jpg</t>
+          <t>M_9_1_1_unmatch_8_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -606,15 +624,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\3_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>M_9_2_I_filler_3_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_9_2_I_filler_3_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -660,15 +684,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\9_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>M_9_3_Q_filler_9_day_sun_busy_MODEL.jpg</t>
+          <t>M_9_3_Q_filler_9_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -714,15 +756,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\1_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>M_9_4_L_filler_1_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_9_4_L_filler_1_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -768,15 +816,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\5_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>M_9_5_5_match_5_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_9_5_5_match_5_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -876,15 +930,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\4_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>M_9_7_B_filler_4_day_sun_busy_MODEL.jpg</t>
+          <t>M_9_7_B_filler_4_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -1038,15 +1110,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\2_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>M_9_10_G_filler_2_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_9_10_G_filler_2_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1092,15 +1170,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\7_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>M_9_11_5_unmatch_7_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_9_11_5_unmatch_7_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -1146,15 +1230,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\5_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>M_9_12_D_filler_5_day_rain_busy_MODEL.jpg</t>
+          <t>M_9_12_D_filler_5_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1200,15 +1302,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\2_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>M_9_13_I_filler_2_day_sun_empty_MODEL.jpg</t>
+          <t>M_9_13_I_filler_2_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -1254,15 +1374,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\4_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>M_9_14_4_match_4_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_9_14_4_match_4_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -1308,15 +1434,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>M_9_15_E_filler_7_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_9_15_E_filler_7_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1470,15 +1602,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\9_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>M_9_18_A_filler_9_day_rain_empty_MODEL.jpg</t>
+          <t>M_9_18_A_filler_9_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1524,15 +1674,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\5_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>M_9_19_J_filler_5_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_9_19_J_filler_5_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1578,15 +1734,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\6_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>M_9_20_6_match_6_day_sun_busy_MODEL.jpg</t>
+          <t>M_9_20_6_match_6_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -1632,15 +1806,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\9_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>M_9_21_R_filler_9_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_9_21_R_filler_9_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1686,15 +1866,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\8_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>M_9_22_6_unmatch_8_day_rain_empty_MODEL.jpg</t>
+          <t>M_9_22_6_unmatch_8_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1848,15 +2046,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\9_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>M_9_25_L_filler_9_day_sun_empty_MODEL.jpg</t>
+          <t>M_9_25_L_filler_9_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -1956,15 +2172,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\0_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>M_9_27_0_match_0_day_rain_busy_MODEL.jpg</t>
+          <t>M_9_27_0_match_0_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -2010,15 +2244,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\7_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>M_9_28_L_filler_7_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_9_28_L_filler_7_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2358,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\3_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>M_9_30_U_filler_3_day_rain_empty_MODEL.jpg</t>
+          <t>M_9_30_U_filler_3_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2280,15 +2538,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\0_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>M_9_33_3_unmatch_0_day_rain_busy_MODEL.jpg</t>
+          <t>M_9_33_3_unmatch_0_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -2334,15 +2610,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\4_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>M_9_34_L_filler_4_day_sun_busy_MODEL.jpg</t>
+          <t>M_9_34_L_filler_4_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2442,15 +2736,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\4_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>M_9_36_B_filler_4_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_9_36_B_filler_4_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2496,15 +2796,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\4_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>M_9_37_C_filler_4_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_9_37_C_filler_4_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2856,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\1_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>M_9_38_T_filler_1_day_sun_busy_MODEL.jpg</t>
+          <t>M_9_38_T_filler_1_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2604,15 +2928,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\7_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>M_9_39_L_filler_7_day_rain_empty_MODEL.jpg</t>
+          <t>M_9_39_L_filler_7_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2658,15 +3000,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\0_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>M_9_40_9_unmatch_0_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_9_40_9_unmatch_0_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2820,15 +3168,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\9_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>M_9_43_9_match_9_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_9_43_9_match_9_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2982,15 +3336,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\4_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>M_9_46_U_filler_4_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_9_46_U_filler_4_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -3036,15 +3396,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\8_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>M_9_47_8_match_8_day_sun_busy_MODEL.jpg</t>
+          <t>M_9_47_8_match_8_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -3090,15 +3468,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\7_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>M_9_48_E_filler_7_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_9_48_E_filler_7_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
